--- a/PA_year1_awardees.xlsx
+++ b/PA_year1_awardees.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="276">
   <si>
     <t xml:space="preserve">state</t>
   </si>
@@ -252,7 +252,7 @@
     <t xml:space="preserve">NON_HOSPITAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: federally qualified health center. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: federally qualified health center. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">OVERRIDE</t>
@@ -303,7 +303,7 @@
     <t xml:space="preserve">Tech &amp; Infrastructure | North Central region</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: continuing-care retirement community, not a hospital. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: continuing-care retirement community, not a hospital. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">North Central</t>
@@ -381,7 +381,7 @@
     <t xml:space="preserve">Counselling Services of Southeastern Erie County dba Corry Counseling of LECOM Health</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: community behavioral health provider; 'County' must not read as a local government. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: community behavioral health provider; 'County' must not read as a local government. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">A one-time infrastructure investment to stabilize the Corry Counseling of LECOM Health facility and expand behavioral health service capacity for rural populations. The funding will support an AI-suppprted documentation sustem to improve efficency, video conferencing equipment, repair of water damage and sewage systems, and repurposing of office spece to support clinical capacity.</t>
@@ -393,7 +393,7 @@
     <t xml:space="preserve">LOW</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: organisational form not stated by the source. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: organisational form not stated by the source. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">This project will replce five air handlers, walk-in refrigeratir and freezer, three elevators, and the basement chiller system. Without these infrastructure upgrades, the ability of PHJM to provide necessary, high-quality care and a proper home for the elderly population of the area would be jeopardized, greatly increasing the chances of negative health outcomes for the community.</t>
@@ -414,7 +414,7 @@
     <t xml:space="preserve">EMS &amp; Transportation | South Central region</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: volunteer ambulance service. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: volunteer ambulance service. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">Purchase of an ambulance</t>
@@ -423,7 +423,7 @@
     <t xml:space="preserve">Wayne Memorial Community Health Centers</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: FQHC affiliated with Wayne Memorial Hospital. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: FQHC affiliated with Wayne Memorial Hospital. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">WMCHC has two minor renovations including in this funding. One of which will increase patient access particularly women’s health and obstetrics in an area (Pike County) where Wayne Memorial Community Health Centers provides the only OB care with the nearest other resources can be an hour away from patients’ homes. The second renovation is adding a gutter system to one office in Wayne County. Heavy rains are deteriorating the pavement and walkways creating a continuous maintenance issue in order provide safe footing entering and exiting. The remainder of the budget is comprised of technology embracing AI and innovation.</t>
@@ -462,7 +462,7 @@
     <t xml:space="preserve">Transitions Healthcare Gettysburg, LLC</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: post-acute / skilled nursing operator. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: post-acute / skilled nursing operator. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">Transitions Healthcare Gettysburg will implement a dedicated non-emergency medical transportation solution through the acquisition of a customized transport van equipped with a specialized stretcher chair system.</t>
@@ -480,7 +480,7 @@
     <t xml:space="preserve">PHYSICIAN_PRACTICE</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: professional corporation; the published name has no period after the C. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: professional corporation; the published name has no period after the C. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">Nulton Diagnostic and Treatment Center, P.C. (NDTC) will implement a centralized technology platform designed to support Rapid Access Psychiatric Services and Community-Based Intensive Treatment (CBIT) across rural Pennsylvania, with initial deployment at its licensed location in Cambria County. The platform will enable real-time referral intake, scheduling, patient tracking, and performance monitoring, and consists of two integrated components: (1) a Rapid Access coordination module that allows referring providers, including emergency departments, crisis response systems, and inpatient psychiatric units, to schedule psychiatric appointments within one business day, and (2) a CBIT management and oversight module that supports providers and managed care organizations in monitoring adherence to the CBIT model and tracking utilization and performance.</t>
@@ -492,7 +492,7 @@
     <t xml:space="preserve">EMS &amp; Transportation | North Central region</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: community behavioral health provider. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: community behavioral health provider. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">The Guidance Center will purchase four vehicles that will enable agency staff to provide safe, reliable transportation to essential healthcare services, including inpatient behavioral health care, crisis stabilization, specialty medical care, and maternal health services, to individuals enrolled in services with the organization. Providing transportation will improve access, reduce non-essential emergency service utilization, support continuity of care, and directlyaddress rural health disparities by removing a significant barrier to care.</t>
@@ -501,7 +501,7 @@
     <t xml:space="preserve">Cornerstone Care, Inc. Mt Morris</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: Cornerstone Care is an FQHC network. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: Cornerstone Care is an FQHC network. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">Cornerstone Care is using funds to expand its capacity to offer pharmacy services at its Community Health Center of Mount Morris site. Cornerstone Care is using new strategies to provide prescription access through a secure vending machine. This innovative equipment allows the health center to fill prescriptions and make them available for our patients during extended hours. The project budget also includes new roofing, a generator, IT equipment upgrades, ADA enhancements, pharmacy upgrades, and replacement of outdated dental and medical equipment. The Mount Morris site serves nearly 2,500 unique patients during more than 5,300 visits annually across service lines.</t>
@@ -516,7 +516,7 @@
     <t xml:space="preserve">Somerset Care Inc dba Meadow View Nursing Center</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: skilled nursing facility. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: skilled nursing facility. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">The project includes the following components: • Replacement of outdated and insufficient ceiling lighting throughout resident rooms, hallways, and common areas • Installation of new, safe, and durable flooring to eliminate current trip hazards and improve mobility and safety • Interior painting of resident rooms, hallways, and common areas to improve the care environment and resident experience • Replacement of aging laundry equipment to improve infection control and operational efficiency • Installation of access control systems at facility entry points and staff areas to enhance resident safety and security • Replacement of resident Transportation vehicles for the facility to be able to transport resident to appointments outside of facility in a rural area where other providers are not available to transport</t>
@@ -540,7 +540,7 @@
     <t xml:space="preserve">EMS &amp; Transportation | Southwest region</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: LIFE (PACE) program operator. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: LIFE (PACE) program operator. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">LIFE Butler County will purchase a new Micro Bird bus with the funding and enhance transportation access.</t>
@@ -597,7 +597,7 @@
     <t xml:space="preserve">Weatherwood Rehabilitation and Healthcare LLC dba Forrest Hills Rehabilitation &amp; Healthcare Center</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: skilled nursing / rehabilitation facility. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: skilled nursing / rehabilitation facility. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">This program payment will fund a renovation and structural improvement project at Weatherwood Rehabilitation and Healthcare Center, a 200-bed skilled nursing facility in Carbon County, Pennsylvania. The project will renovate the facility's six resident-care areas (Main Lobby/Entrance Corridor, Resident Room Corridor, Resident Rooms, Resident Bathrooms, Dining Room, and Gym/Physical Therapy Room) to address resident safety, infection control, life-safety compliance, and rehabilitation capacity needs.</t>
@@ -627,7 +627,7 @@
     <t xml:space="preserve">EMS &amp; Transportation | Central region</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: opioid treatment program; the published name is truncated mid-DBA. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: opioid treatment program; the published name is truncated mid-DBA. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">Habit Opco, LLC DBA Watsontown CTC will use funding to purchase and implement a passenger transportation van that will expand access to medication-assisted treatment (MAT), counseling, and behavioral health services for individuals living in rural and underserved Pennsylvania communities.</t>
@@ -636,7 +636,7 @@
     <t xml:space="preserve">Center for Behavioral Health-HA, LLC dba Lewistown Comprehensive Treatment Center</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: opioid treatment program. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: opioid treatment program. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">Center for Behavioral Health-HA, LLC DBA Lewistown Comprehensive Treatment Center (Lewistown CTC) will use funding to purchase and implement a passenger transportation van that will expand access to medication-assisted treatment (MAT), counseling, and behavioral health services for individuals living in rural and underserved Pennsylvania communities.</t>
@@ -654,7 +654,7 @@
     <t xml:space="preserve">Center for Behavioral Health-PA, LLC dba Cranberry Township Comprehensive Treatment Center</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: opioid treatment program; 'Township' must not read as a local government. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: opioid treatment program; 'Township' must not read as a local government. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">Center for Behavioral Health-, LLC DBA Cranberry Township CTC will receive funding (1) to purchase and implement a passenger transportation van that will expand access to medication-assisted treatment (MAT), counseling, and behavioral health services for individuals living in rural and underserved Pennsylvania communities, and (2) for facility enhancement funding to support critical security infrastructure improvements focused on patient safety, staff protection, operational oversight, regulatory compliance, and long-term operational sustainability. The proposed project includes installation of additional surveillance cameras within the dispensary area, expanded exterior camera coverage upgrades, and installation of surveillance coverage within administrative areas that were not included in the facility’s prior security system upgrade.</t>
@@ -690,7 +690,7 @@
     <t xml:space="preserve">VENDOR_OR_CONTRACTOR</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: retail pharmacy supplying, not receiving, hospital care. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: retail pharmacy supplying, not receiving, hospital care. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">Gaughn's Drug Store will use the funding to renovate the existing physical space to allow for greater capacity to conduct in-person clinical visits in the pharmacy, to leverage expanded technology to implement telehealth for pharmacy services (initially) and for expanded primary care services or even specialty services in the future via partnerships with local or national partners, and to use technology and upgraded infrastructure to improve and expand operational capacity for traditional prescription dispensing and adherence packaging.</t>
@@ -711,7 +711,10 @@
     <t xml:space="preserve">Wyoming County Healthcare Center II dba Wyoming County Healthcare Center</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: county-affiliated skilled nursing facility, not a hospital. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">IN_KIND_BENEFIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curated override: county-affiliated skilled nursing facility, not a hospital. §10.2 IN_KIND_BENEFIT: the recipient is not a hospital and keeps the funds, and the source names hospitals among the parties the funded work serves. These dollars must never enter a 'funds distributed to hospitals' total; they are kept visible rather than discarded. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">Funding will support critical electrical infrastructure upgrades that are essential to the continued operation of healthcare services in a rural county without a hospital. WCHC is an electric-dependent facility housing 14 healthcare-related organizations that collectively supported approximately 46,000 patient visits in 2025. The project will replace major electrical distribution infrastructure serving the facility, including the main electrical switchboard “MDS,” distribution switchboards and motor control centers, and selected panelboards and transformers. These systems support the continued operation of healthcare providers, diagnostic services, emergency response functions, telecommunications and data systems, life-safety systems, elevators, environmental controls, and other building systems required to maintain safe and reliable access to care.</t>
@@ -720,7 +723,7 @@
     <t xml:space="preserve">Cameron County Ambulance Service</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: county ambulance service; the EMS rule must beat the local-government rule. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: county ambulance service; the EMS rule must beat the local-government rule. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">Program funds will be used to support critical facility improvements at the Cameron County Ambulance Service (CCAS) aimed at expanding and modernizing our existing conference and training space. The purpose of this project is to convert and expand the current training room into a more functional, flexible, and professional-grade educational environment capable of supporting EMT and Advanced EMT (AEMT) instruction, hands-on skills development, and ongoing continuing education requirements.</t>
@@ -729,7 +732,7 @@
     <t xml:space="preserve">Board of Directors of the Rouse Estate dba Warren County Rouse Home</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: skilled nursing facility; 'County' must not read as a local government. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: skilled nursing facility; 'County' must not read as a local government. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">The Rouse Home will use funding to purchase 120 specialized low-profile beds designed to improve resident safety, clinical outcomes, and dignity for skilled nursing residents. These beds are equipped with advanced technology that allows the bed frame to lower completely to floor level, significantly reducing the risk of falls and injuries associated with bed-related incidents. Research and manufacturer data demonstrate these beds can reduce falls by approximately 55% and reduce bed fall injuries by up to 100%.</t>
@@ -741,7 +744,7 @@
     <t xml:space="preserve">LOCAL_GOVT_OR_PUBLIC_HEALTH</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: Columbia-Montour-Snyder-Union joint-county behavioral health authority. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: Columbia-Montour-Snyder-Union joint-county behavioral health authority. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">CMSU will use the funds to replace aging Information Technology equipment that is at or nearing its end of life. These devices are used by CMSU staff who are in the field, meeting residents in their home eliminating the transportation barriers that many residents experience. These mobile devices afford CMSU staff connection to clients and allow clients to connect with other needed services. As these devices age, the ability to operate effectively and securely is compromised, creating undue stress on an already vulnerable workforce. These devices also allow staff to remain virtually connected to their home office, supervisor support, and training. CMSU will also purchase a passenger van to replace an aging model that has accrued high mileage. The current van is less reliable, decreasing quality and continuity of care.</t>
@@ -753,7 +756,7 @@
     <t xml:space="preserve">Maternal Health | South Central region</t>
   </si>
   <si>
-    <t xml:space="preserve">Curated override: freestanding birth center. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not state that hospitals receive or use the funded activity. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
+    <t xml:space="preserve">Curated override: freestanding birth center. §10.2 NON_HOSPITAL: the named recipient is not a hospital (§0.3a -- judged on the recipient, not the activity), and the source does not mention hospitals anywhere in the funded work. Source: PA DHS announced 66 authorized projects on 2026-07-23; the names and amounts are from the DHS Rural Health Selected Projects page it links to. Distribution is pending approval of selected projects, so this is an intent to award.</t>
   </si>
   <si>
     <t xml:space="preserve">Maternal Health</t>
@@ -7029,13 +7032,13 @@
       </c>
       <c r="V62"/>
       <c r="W62" t="s">
-        <v>78</v>
+        <v>232</v>
       </c>
       <c r="X62" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="Y62" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Z62" t="s">
         <v>49</v>
@@ -7065,7 +7068,7 @@
         <v>55</v>
       </c>
       <c r="AI62" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="63">
@@ -7076,7 +7079,7 @@
         <v>62</v>
       </c>
       <c r="C63" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D63" t="n">
         <v>88068.72</v>
@@ -7130,7 +7133,7 @@
         <v>75</v>
       </c>
       <c r="Y63" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Z63" t="s">
         <v>49</v>
@@ -7160,7 +7163,7 @@
         <v>81</v>
       </c>
       <c r="AI63" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="64">
@@ -7171,7 +7174,7 @@
         <v>63</v>
       </c>
       <c r="C64" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D64" t="n">
         <v>370886</v>
@@ -7225,7 +7228,7 @@
         <v>75</v>
       </c>
       <c r="Y64" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Z64" t="s">
         <v>49</v>
@@ -7255,7 +7258,7 @@
         <v>55</v>
       </c>
       <c r="AI64" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="65">
@@ -7266,13 +7269,13 @@
         <v>64</v>
       </c>
       <c r="C65" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D65" t="n">
         <v>166443</v>
       </c>
       <c r="E65" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F65" t="s">
         <v>75</v>
@@ -7320,7 +7323,7 @@
         <v>75</v>
       </c>
       <c r="Y65" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Z65" t="s">
         <v>49</v>
@@ -7350,7 +7353,7 @@
         <v>55</v>
       </c>
       <c r="AI65" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="66">
@@ -7361,7 +7364,7 @@
         <v>65</v>
       </c>
       <c r="C66" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D66" t="n">
         <v>467410</v>
@@ -7373,7 +7376,7 @@
         <v>75</v>
       </c>
       <c r="G66" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H66" t="s">
         <v>38</v>
@@ -7415,7 +7418,7 @@
         <v>75</v>
       </c>
       <c r="Y66" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Z66" t="s">
         <v>49</v>
@@ -7436,16 +7439,16 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG66" t="s">
         <v>89</v>
       </c>
       <c r="AH66" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AI66" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="67">
@@ -7456,7 +7459,7 @@
         <v>66</v>
       </c>
       <c r="C67" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D67" t="n">
         <v>452800</v>
@@ -7540,7 +7543,7 @@
         <v>55</v>
       </c>
       <c r="AI67" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -7556,106 +7559,106 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B3" t="s">
         <v>255</v>
-      </c>
-      <c r="B3" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B12" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
